--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536119_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536119_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,7 +1538,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. GONZÁLEZ RAMÍREZ</t>
+          <t>N. BILAMU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1550,64 +1550,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7451</v>
+        <v>2.7223</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7451</v>
+        <v>3.2152</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0.4929</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7451</v>
+        <v>3.1243</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9226</v>
+        <v>2.6674</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8226</v>
+        <v>0.4568</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7451</v>
+        <v>4.8758</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9226</v>
+        <v>2.9482</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8226</v>
+        <v>1.9276</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-1.7516</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.2808</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.4708</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.6805</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.9643</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.2838</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. BILAMU</t>
+          <t>N. PETRONE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7223</v>
+        <v>2.7049</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2152</v>
+        <v>3.1333</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4929</v>
+        <v>-0.4284</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1243</v>
+        <v>0.4277</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6674</v>
+        <v>1.0159</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4568</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>4.8758</v>
+        <v>1.6447</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9482</v>
+        <v>1.7016</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9276</v>
+        <v>-0.057</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7516</v>
+        <v>-1.2169</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2808</v>
+        <v>-0.6857</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4708</v>
+        <v>-0.5312</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0.585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9749</v>
+        <v>0.585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6805</v>
+        <v>0.1407</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9643</v>
+        <v>-0.3415</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2838</v>
+        <v>0.4822</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2786</v>
+        <v>1.5515</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2786</v>
+        <v>1.8301</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. PETRONE</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7049</v>
+        <v>1.3612</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1333</v>
+        <v>2.2363</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4284</v>
+        <v>-0.8752</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4277</v>
+        <v>4.0214</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0159</v>
+        <v>0.2614</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5881999999999999</v>
+        <v>3.7601</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6447</v>
+        <v>5.1008</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7016</v>
+        <v>0.8161</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.057</v>
+        <v>4.2847</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2169</v>
+        <v>-1.0794</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6857</v>
+        <v>-0.5547</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5312</v>
+        <v>-0.5246</v>
       </c>
       <c r="P16" t="n">
-        <v>0.585</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R16" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1407</v>
+        <v>-0.6602</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3415</v>
+        <v>-0.9146</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4822</v>
+        <v>0.2544</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5515</v>
+        <v>-1.2201</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>R. ROTCENKOVS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3612</v>
+        <v>-0.9911</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2363</v>
+        <v>0.0587</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8752</v>
+        <v>-1.0498</v>
       </c>
       <c r="G17" t="n">
-        <v>4.0214</v>
+        <v>-1.301</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2614</v>
+        <v>-1.139</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7601</v>
+        <v>-0.162</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1008</v>
+        <v>-0.012</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8161</v>
+        <v>-0.66</v>
       </c>
       <c r="L17" t="n">
-        <v>4.2847</v>
+        <v>0.648</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0794</v>
+        <v>-1.289</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5547</v>
+        <v>-0.4789</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5246</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7799</v>
+        <v>0.195</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1699</v>
+        <v>0.195</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6602</v>
+        <v>0.1149</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9146</v>
+        <v>0.0707</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2544</v>
+        <v>0.0442</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2201</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2201</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. ROTCENKOVS</t>
+          <t>K. EZEAGU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9911</v>
+        <v>-1.5725</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0587</v>
+        <v>2.6623</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0498</v>
+        <v>-4.2347</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.301</v>
+        <v>1.0799</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.139</v>
+        <v>1.3827</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.162</v>
+        <v>-0.3028</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.012</v>
+        <v>2.5707</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.66</v>
+        <v>2.2062</v>
       </c>
       <c r="L18" t="n">
-        <v>0.648</v>
+        <v>0.3645</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.289</v>
+        <v>-1.4908</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4789</v>
+        <v>-0.8235</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6673</v>
       </c>
       <c r="P18" t="n">
-        <v>0.195</v>
+        <v>0.585</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.195</v>
+        <v>0.585</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1149</v>
+        <v>0.1443</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0707</v>
+        <v>-0.187</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0442</v>
+        <v>0.3313</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-3.3816</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-3.6602</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. EZEAGU</t>
+          <t>A. TAMAYO LESMES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5725</v>
+        <v>-1.7931</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6623</v>
+        <v>-2.4232</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.2347</v>
+        <v>0.6301</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0799</v>
+        <v>-3.2232</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3827</v>
+        <v>-3.7318</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3028</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5707</v>
+        <v>-2.006</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2062</v>
+        <v>-2.767</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3645</v>
+        <v>0.7611</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4908</v>
+        <v>-1.2172</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8235</v>
+        <v>-0.9648</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6673</v>
+        <v>-0.2524</v>
       </c>
       <c r="P19" t="n">
-        <v>0.585</v>
+        <v>1.5599</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.585</v>
+        <v>1.5599</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1443</v>
+        <v>-0.1298</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.187</v>
+        <v>-0.4173</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3313</v>
+        <v>0.2874</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.3816</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6602</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. TAMAYO LESMES</t>
+          <t>W. TSAFACK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7931</v>
+        <v>-1.8322</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4232</v>
+        <v>-0.3978</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6301</v>
+        <v>-1.4344</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2232</v>
+        <v>-0.2028</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.7318</v>
+        <v>1.2745</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5086000000000001</v>
+        <v>-1.4774</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.006</v>
+        <v>0.8697</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.767</v>
+        <v>0.8697</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7611</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2172</v>
+        <v>-1.0725</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9648</v>
+        <v>0.4049</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2524</v>
+        <v>-1.4774</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5599</v>
+        <v>0.195</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5599</v>
+        <v>0.195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1298</v>
+        <v>-0.6042999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4173</v>
+        <v>-0.6045</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2874</v>
+        <v>0.0002</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6629</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. TSAFACK</t>
+          <t>H. SANTA CRUZ CARDENAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8322</v>
+        <v>-2.185</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3978</v>
+        <v>-0.3319</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4344</v>
+        <v>-1.8531</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2028</v>
+        <v>-0.6761</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2745</v>
+        <v>0.9618</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4774</v>
+        <v>-1.638</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8697</v>
+        <v>0.7491</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8697</v>
+        <v>1.9886</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.2395</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0725</v>
+        <v>-1.4252</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4049</v>
+        <v>-1.0268</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4774</v>
+        <v>-0.3984</v>
       </c>
       <c r="P21" t="n">
         <v>0.195</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R21" t="n">
-        <v>0.195</v>
+        <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.4838</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6045</v>
+        <v>-0.3847</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0002</v>
+        <v>-0.0992</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2201</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6629</v>
+        <v>0.2786</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5571</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. SANTA CRUZ CARDENAL</t>
+          <t>B. GONZALEZ RAMIREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.185</v>
+        <v>-2.3246</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3319</v>
+        <v>-1.7796</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8531</v>
+        <v>-0.545</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6761</v>
+        <v>-0.746</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9618</v>
+        <v>0.4789</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.638</v>
+        <v>-1.2249</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7491</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9886</v>
+        <v>0.6891</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2395</v>
+        <v>-0.697</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4252</v>
+        <v>-0.7381</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0268</v>
+        <v>-0.2102</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3984</v>
+        <v>-0.5279</v>
       </c>
       <c r="P22" t="n">
-        <v>0.195</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4838</v>
+        <v>-0.3586</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3847</v>
+        <v>-0.7968</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0992</v>
+        <v>0.4382</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2201</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4986</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. GONZALEZ RAMIREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0698</v>
+        <v>-10.646</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5248</v>
+        <v>6.962799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.545</v>
+        <v>-17.6087</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4911</v>
+        <v>0.01719999999999988</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4436</v>
+        <v>4.7806</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0475</v>
+        <v>-4.7636</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.753</v>
+        <v>15.8846</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2334</v>
+        <v>9.957800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.5196</v>
+        <v>5.927</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7381</v>
+        <v>-15.8676</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2102</v>
+        <v>-5.177</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5279</v>
+        <v>-10.6904</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9749</v>
+        <v>-6.8245</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9749</v>
+        <v>8.7744</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3586</v>
+        <v>-1.858</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7968</v>
+        <v>-4.6575</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4382</v>
+        <v>2.7993</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2201</v>
+        <v>-10.755</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.5601</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536119_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-10.6461</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6.962700000000003</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-17.6087</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.01720000000000077</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.7807</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-4.7636</v>
-      </c>
-      <c r="J26" t="n">
-        <v>15.8846</v>
-      </c>
-      <c r="K26" t="n">
-        <v>9.9579</v>
-      </c>
-      <c r="L26" t="n">
-        <v>5.927</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-15.8676</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-5.177</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-10.6904</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-6.8245</v>
-      </c>
-      <c r="R26" t="n">
-        <v>8.7744</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-1.858</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-4.657500000000001</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.7993</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-10.755</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.5601</v>
-      </c>
-      <c r="X26" t="n">
         <v>-13.3149</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
